--- a/dummy_data/flow3/haider_corrections_response.xlsx
+++ b/dummy_data/flow3/haider_corrections_response.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Name Validation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DOB Mistakes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Missing Mobile Numbers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CMS Data Integration" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Missing Mobile Numbers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CMS Data Integration" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -528,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,41 +538,49 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ACCOUNT_HOLDER_DOB</t>
+          <t>PHONE_NUMBER</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9000008</t>
+          <t>9000015</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1990-05-05 00:00:00</t>
+          <t>07701234567</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9000009</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>9000016</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07709876543</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9000010</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1985-11-20 00:00:00</t>
-        </is>
-      </c>
+          <t>9000017</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9000020</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -586,72 +593,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ACCOUNT_NUMBER</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PHONE_NUMBER</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>9000015</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>07701234567</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>9000016</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07709876543</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9000017</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9000020</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/dummy_data/flow3/haider_corrections_response.xlsx
+++ b/dummy_data/flow3/haider_corrections_response.xlsx
@@ -441,10 +441,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>9000003</t>
-        </is>
+      <c r="A2" t="n">
+        <v>9000003</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -463,10 +461,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>9000004</t>
-        </is>
+      <c r="A3" t="n">
+        <v>9000004</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -485,10 +481,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9000005</t>
-        </is>
+      <c r="A4" t="n">
+        <v>9000005</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -507,10 +501,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9000017</t>
-        </is>
+      <c r="A5" t="n">
+        <v>9000017</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
@@ -543,42 +535,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>9000015</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>07701234567</t>
-        </is>
+      <c r="A2" t="n">
+        <v>9000015</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7701234567</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>9000016</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07709876543</t>
-        </is>
+      <c r="A3" t="n">
+        <v>9000016</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7709876543</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9000017</t>
-        </is>
+      <c r="A4" t="n">
+        <v>9000017</v>
       </c>
       <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9000020</t>
-        </is>
+      <c r="A5" t="n">
+        <v>9000020</v>
       </c>
       <c r="B5" t="inlineStr"/>
     </row>
@@ -629,14 +609,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>9000001</t>
-        </is>
+      <c r="A2" t="n">
+        <v>9000001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4111222233334444</t>
+          <t>400044******6666</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -661,10 +639,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>9000002</t>
-        </is>
+      <c r="A3" t="n">
+        <v>9000002</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
@@ -673,10 +649,8 @@
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9000003</t>
-        </is>
+      <c r="A4" t="n">
+        <v>9000003</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
@@ -685,10 +659,8 @@
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9000004</t>
-        </is>
+      <c r="A5" t="n">
+        <v>9000004</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
@@ -697,10 +669,8 @@
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>9000005</t>
-        </is>
+      <c r="A6" t="n">
+        <v>9000005</v>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
@@ -709,10 +679,8 @@
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>9000006</t>
-        </is>
+      <c r="A7" t="n">
+        <v>9000006</v>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
@@ -721,10 +689,8 @@
       <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>9000007</t>
-        </is>
+      <c r="A8" t="n">
+        <v>9000007</v>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
@@ -733,10 +699,8 @@
       <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>9000008</t>
-        </is>
+      <c r="A9" t="n">
+        <v>9000008</v>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -745,10 +709,8 @@
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9000009</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9000009</v>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -757,10 +719,8 @@
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>9000010</t>
-        </is>
+      <c r="A11" t="n">
+        <v>9000010</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -769,10 +729,8 @@
       <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>9000011</t>
-        </is>
+      <c r="A12" t="n">
+        <v>9000011</v>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -781,10 +739,8 @@
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>9000012</t>
-        </is>
+      <c r="A13" t="n">
+        <v>9000012</v>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -793,10 +749,8 @@
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>9000013</t>
-        </is>
+      <c r="A14" t="n">
+        <v>9000013</v>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -805,10 +759,8 @@
       <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>9000014</t>
-        </is>
+      <c r="A15" t="n">
+        <v>9000014</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -817,10 +769,8 @@
       <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>9000015</t>
-        </is>
+      <c r="A16" t="n">
+        <v>9000015</v>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
@@ -829,10 +779,8 @@
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>9000016</t>
-        </is>
+      <c r="A17" t="n">
+        <v>9000016</v>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
@@ -841,10 +789,8 @@
       <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>9000017</t>
-        </is>
+      <c r="A18" t="n">
+        <v>9000017</v>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
@@ -853,14 +799,12 @@
       <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>9000018</t>
-        </is>
+      <c r="A19" t="n">
+        <v>9000018</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4111222233335555</t>
+          <t>400011******3333</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -885,14 +829,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>9000019</t>
-        </is>
+      <c r="A20" t="n">
+        <v>9000019</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4111222233336666</t>
+          <t>400077******9999</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -917,10 +859,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>9000020</t>
-        </is>
+      <c r="A21" t="n">
+        <v>9000020</v>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
